--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87195</v>
+        <v>87403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87403</v>
+        <v>87405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87405</v>
+        <v>87408</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3189,32 +3189,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132761003</v>
+        <v>137282769</v>
       </c>
       <c r="B25" t="n">
-        <v>56539</v>
+        <v>107905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>206004</v>
+        <v>219686</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3222,27 +3222,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bjurfors gamla tomt, Vstm</t>
+          <t>Riddarhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546211</v>
+        <v>528193</v>
       </c>
       <c r="R25" t="n">
-        <v>6628964</v>
+        <v>6629755</v>
       </c>
       <c r="S25" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3261,27 +3253,32 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Gunnilbo</t>
+          <t>Skinnskatteberg</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,65 +3293,69 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132761003</t>
+          <t>https://artportalen.se/Sighting/137282769</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113273795</v>
+        <v>137282816</v>
       </c>
       <c r="B26" t="n">
-        <v>79946</v>
+        <v>98256</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra kavelbromossen, Vstm</t>
+          <t>Forshammar, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535096</v>
+        <v>528069</v>
       </c>
       <c r="R26" t="n">
-        <v>6625338</v>
+        <v>6629388</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3378,12 +3379,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3394,29 +3410,255 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>tallstubbe</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282816</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132761003</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56539</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bjurfors gamla tomt, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>546211</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6628964</v>
+      </c>
+      <c r="S27" t="n">
+        <v>36</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132761003</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>113273795</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Södra kavelbromossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>535096</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6625338</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
+      <c r="AY28" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113273795</t>
         </is>
@@ -3449,6 +3691,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87408</v>
+        <v>87418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137282769</v>
       </c>
       <c r="B25" t="n">
-        <v>107905</v>
+        <v>107926</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137282816</v>
       </c>
       <c r="B26" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87418</v>
+        <v>87419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137282769</v>
       </c>
       <c r="B25" t="n">
-        <v>107926</v>
+        <v>107927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137282816</v>
       </c>
       <c r="B26" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87419</v>
+        <v>87422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137282769</v>
       </c>
       <c r="B25" t="n">
-        <v>107927</v>
+        <v>107932</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137282816</v>
       </c>
       <c r="B26" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -3192,7 +3192,7 @@
         <v>137282769</v>
       </c>
       <c r="B25" t="n">
-        <v>107932</v>
+        <v>107935</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137282816</v>
       </c>
       <c r="B26" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87422</v>
+        <v>87427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137282769</v>
       </c>
       <c r="B25" t="n">
-        <v>107935</v>
+        <v>107941</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137282816</v>
       </c>
       <c r="B26" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -3192,7 +3192,7 @@
         <v>137282769</v>
       </c>
       <c r="B25" t="n">
-        <v>107941</v>
+        <v>107942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87427</v>
+        <v>87438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137282769</v>
       </c>
       <c r="B25" t="n">
-        <v>107942</v>
+        <v>107954</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137282816</v>
       </c>
       <c r="B26" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87438</v>
+        <v>87439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137282769</v>
       </c>
       <c r="B25" t="n">
-        <v>107954</v>
+        <v>107955</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137282816</v>
       </c>
       <c r="B26" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87439</v>
+        <v>87442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>137282769</v>
       </c>
       <c r="B25" t="n">
-        <v>107955</v>
+        <v>107958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>137282816</v>
       </c>
       <c r="B26" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2967,48 +2967,60 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>75360630</v>
+        <v>137510616</v>
       </c>
       <c r="B23" t="n">
-        <v>93189</v>
+        <v>57221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lien, S, Vstm</t>
+          <t>Grusvägen förbi Dramboln, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528045</v>
+        <v>544134</v>
       </c>
       <c r="R23" t="n">
-        <v>6629670</v>
+        <v>6632374</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,17 +3039,17 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Skinnskatteberg</t>
+          <t>Gunnilbo</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2018-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2018-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,61 +3061,42 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>sandtallskog</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Svampinventering i sandtallskogar</t>
-        </is>
-      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75360630</t>
+          <t>https://artportalen.se/Sighting/137510616</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>75360629</v>
+        <v>75360630</v>
       </c>
       <c r="B24" t="n">
-        <v>93193</v>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3113,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528048</v>
+        <v>528045</v>
       </c>
       <c r="R24" t="n">
-        <v>6629674</v>
+        <v>6629670</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3183,16 +3176,16 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75360629</t>
+          <t>https://artportalen.se/Sighting/75360630</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137282769</v>
+        <v>75360629</v>
       </c>
       <c r="B25" t="n">
-        <v>107958</v>
+        <v>93193</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,38 +3193,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219686</v>
+        <v>4363</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Riddarhyttan, Vstm</t>
+          <t>Lien, S, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528193</v>
+        <v>528048</v>
       </c>
       <c r="R25" t="n">
-        <v>6629755</v>
+        <v>6629674</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3258,27 +3247,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>08:35</t>
+          <t>2018-10-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2018-10-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3289,31 +3263,40 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Svampinventering i sandtallskogar</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137282769</t>
+          <t>https://artportalen.se/Sighting/75360629</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137282816</v>
+        <v>137282769</v>
       </c>
       <c r="B26" t="n">
-        <v>98296</v>
+        <v>107958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,16 +3304,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>219686</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3345,14 +3328,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Forshammar, Vstm</t>
+          <t>Riddarhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528069</v>
+        <v>528193</v>
       </c>
       <c r="R26" t="n">
-        <v>6629388</v>
+        <v>6629755</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3384,7 +3367,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3394,7 +3377,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3425,38 +3408,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137282816</t>
+          <t>https://artportalen.se/Sighting/137282769</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132761003</v>
+        <v>137282816</v>
       </c>
       <c r="B27" t="n">
-        <v>56539</v>
+        <v>98296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3464,27 +3447,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bjurfors gamla tomt, Vstm</t>
+          <t>Forshammar, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546211</v>
+        <v>528069</v>
       </c>
       <c r="R27" t="n">
-        <v>6628964</v>
+        <v>6629388</v>
       </c>
       <c r="S27" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3503,27 +3478,32 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Gunnilbo</t>
+          <t>Skinnskatteberg</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3538,27 +3518,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132761003</t>
+          <t>https://artportalen.se/Sighting/137282816</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113273795</v>
+        <v>132761003</v>
       </c>
       <c r="B28" t="n">
-        <v>79946</v>
+        <v>56539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3566,37 +3546,49 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>206004</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Södra kavelbromossen, Vstm</t>
+          <t>Bjurfors gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>535096</v>
+        <v>546211</v>
       </c>
       <c r="R28" t="n">
-        <v>6625338</v>
+        <v>6628964</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3615,17 +3607,27 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Skinnskatteberg</t>
+          <t>Gunnilbo</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3636,29 +3638,131 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>tallstubbe</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132761003</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113273795</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Södra kavelbromossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>535096</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6625338</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr">
+      <c r="AY29" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113273795</t>
         </is>
@@ -3693,6 +3797,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -1244,7 +1244,7 @@
         <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87442</v>
+        <v>87446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>137510616</v>
       </c>
       <c r="B23" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,6 +3062,16 @@
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristina Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristina Falk</t>
+        </is>
+      </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
@@ -3296,7 +3306,7 @@
         <v>137282769</v>
       </c>
       <c r="B26" t="n">
-        <v>107958</v>
+        <v>107964</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,7 +3427,7 @@
         <v>137282816</v>
       </c>
       <c r="B27" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
